--- a/data/_test/aggregate/xls_score.xlsx
+++ b/data/_test/aggregate/xls_score.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\P42587\Documents\GitHub\pyXLMS\data\_test\aggregate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Micha\Documents\GitHub\pyXLMS\data\_test\aggregate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4777534C-CD4E-4509-A525-4CEC02AD2BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7034790B-31F5-4E05-B4DE-B3BDD45E890D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5970" yWindow="4170" windowWidth="31770" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
     <t>2;1</t>
   </si>
   <si>
-    <t>Score</t>
+    <t>Crosslink Score</t>
   </si>
 </sst>
 </file>
